--- a/content/post/drafts/season-prediction/ladies_predictions-with-selected-features.xlsx
+++ b/content/post/drafts/season-prediction/ladies_predictions-with-selected-features.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -66,1651 +66,1693 @@
     <t xml:space="preserve">Top30_American_Odds</t>
   </si>
   <si>
+    <t xml:space="preserve">Linn Svahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1175</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jonna Sundling</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linn Svahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6%</t>
+    <t xml:space="preserve">91.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma Ribom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosie Brennan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0%</t>
   </si>
   <si>
     <t xml:space="preserve">38.5%</t>
   </si>
   <si>
-    <t xml:space="preserve">77.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-310</t>
+    <t xml:space="preserve">72.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frida Karlsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessie Diggins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kerttu Niskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Carl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heidi Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krista Pärmäkoski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.1%</t>
   </si>
   <si>
     <t xml:space="preserve">+159</t>
   </si>
   <si>
-    <t xml:space="preserve">-339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jessie Diggins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.7%</t>
+    <t xml:space="preserve">+433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katharina Hennig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotta Udnes Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanna Matintalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moa Ilar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadine Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiril Udnes Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Kjersti Kalvå</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebba Andersson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pia Fink</t>
   </si>
   <si>
     <t xml:space="preserve">19.1%</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-280</t>
+    <t xml:space="preserve">5.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7%</t>
   </si>
   <si>
     <t xml:space="preserve">+423</t>
   </si>
   <si>
-    <t xml:space="preserve">+116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frida Karlsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kerttu Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emma Ribom</t>
+    <t xml:space="preserve">+4829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maja Dahlqvist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristine Stavås Skistad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astrid Øyre Slind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Gimmler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa Stadlober</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Kyllönen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia Kern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moa Lundgren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanna Hagström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathilde Myhrvold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1%</t>
   </si>
   <si>
     <t xml:space="preserve">65.2%</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosie Brennan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heidi Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Carl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katharina Hennig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krista Pärmäkoski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ebba Andersson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5%</t>
+    <t xml:space="preserve">+1593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margrethe Bergane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sophia Laukli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delphine Claudel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katerina Janatova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricijia Eiduka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmi Joensuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flora Dolci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coletta Rydzek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lena Keck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofie Krehl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadezhda Stepashkina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisa Lohmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kseniya Shalygina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadja Kälin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katri Lylynperä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caterina Ganz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katherine Sauerbrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desiree Steiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darya Ryazhko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole Monsorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novie McCabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samantha Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Weber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathrine Stewart-Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliette Ducordeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesca Franchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keidy Kaasiku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamila Makhmutova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofia Henriksson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Mandeljc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lea Fischer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tereza Beranova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melissa Gal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitija Auzina</t>
   </si>
   <si>
     <t xml:space="preserve">5.7%</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Matintalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristine Stavås Skistad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadine Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiril Udnes Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Kjersti Kalvå</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa Stadlober</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrid Øyre Slind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lotta Udnes Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa Ilar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maja Dahlqvist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delphine Claudel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricijia Eiduka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pia Fink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katerina Janatova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margrethe Bergane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Kyllönen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sophia Laukli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flora Dolci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Gimmler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-261</t>
+    <t xml:space="preserve">+8242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alina Meier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+274</t>
   </si>
   <si>
     <t xml:space="preserve">Anna Comarella</t>
   </si>
   <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katherine Sauerbrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisa Lohmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novie McCabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofia Henriksson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathrine Stewart-Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadja Kälin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesca Franchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juliette Ducordeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0%</t>
+    <t xml:space="preserve">9.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora Antosova</t>
   </si>
   <si>
     <t xml:space="preserve">8.9%</t>
   </si>
   <si>
-    <t xml:space="preserve">+1577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Hagström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathilde Myhrvold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmi Joensuu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coletta Rydzek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julia Kern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anja Mandeljc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa Lundgren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6453</t>
+    <t xml:space="preserve">+11976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alayna Sonnesyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2624</t>
   </si>
   <si>
     <t xml:space="preserve">Tiia Olkkonen</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lena Keck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caterina Ganz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+8372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofie Krehl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tereza Beranova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicole Monsorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katri Lylynperä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desiree Steiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kseniya Shalygina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbora Antosova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+995</t>
+    <t xml:space="preserve">+8850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmin Kähärä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna Melnik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izabela Marcisz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonjaa Schmidt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1376</t>
   </si>
   <si>
     <t xml:space="preserve">Lena Quintin</t>
   </si>
   <si>
-    <t xml:space="preserve">+3807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmin Kähärä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadezhda Stepashkina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alina Meier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anja Weber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lea Fischer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darya Ryazhko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melissa Gal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izabela Marcisz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamila Makhmutova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonjaa Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1447</t>
+    <t xml:space="preserve">13.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilma Ryytty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliane Gagnon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+906</t>
   </si>
   <si>
     <t xml:space="preserve">Amelia Wells</t>
   </si>
   <si>
-    <t xml:space="preserve">+4330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samantha Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitija Auzina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keidy Kaasiku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2897</t>
+    <t xml:space="preserve">+10211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisa Ingesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+11863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2061</t>
   </si>
   <si>
     <t xml:space="preserve">Kaidy Kaasiku</t>
   </si>
   <si>
-    <t xml:space="preserve">+4491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna Melnik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vilma Ryytty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liliane Gagnon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisa Ingesson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+11134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alayna Sonnesyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+11271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2766</t>
+    <t xml:space="preserve">+10517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12690</t>
   </si>
   <si>
     <t xml:space="preserve">Target</t>
@@ -1722,25 +1764,25 @@
     <t xml:space="preserve">TopThree</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points, Prev_Sprint_C, Prev_Distance_C, Prev_Sprint_F</t>
+    <t xml:space="preserve">Prev_Sprint_C, Prev_Distance_F, Prev_Distance</t>
   </si>
   <si>
     <t xml:space="preserve">Top5</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points, Prev_Sprint, Prev_Distance</t>
+    <t xml:space="preserve">Prev_Distance_F, Prev_C, Prev_Sprint, Prev_Distance, Prev_Pelo</t>
   </si>
   <si>
     <t xml:space="preserve">Top10</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points, Prev_C, Prev_Sprint_F, Prev_Sprint_C, Prev_Distance</t>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points, Prev_Sprint, Prev_Distance_F, Prev_Sprint_F, Prev_Distance_C</t>
   </si>
   <si>
     <t xml:space="preserve">Top30</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points, Prev_Distance_F, Prev_Distance_C, Prev_F, Prev_Sprint</t>
+    <t xml:space="preserve">Prev_Distance, Prev_Distance_F, Prev_C, Prev_Sprint</t>
   </si>
 </sst>
 </file>
@@ -2145,31 +2187,31 @@
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="I2" t="s">
         <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>2.26</v>
+        <v>3.66</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="M2" t="s">
         <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="O2" t="s">
         <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Q2" t="s">
         <v>26</v>
@@ -2198,25 +2240,25 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="s">
         <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="K3" t="s">
         <v>33</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="s">
         <v>34</v>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="s">
         <v>32</v>
@@ -2233,60 +2275,60 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="K4" t="s">
         <v>42</v>
       </c>
-      <c r="J4" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="s">
         <v>43</v>
       </c>
-      <c r="L4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q4" t="s">
         <v>44</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>47</v>
@@ -2304,31 +2346,31 @@
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="I5" t="s">
         <v>51</v>
       </c>
       <c r="J5" t="n">
-        <v>7.06</v>
+        <v>3.13</v>
       </c>
       <c r="K5" t="s">
         <v>52</v>
       </c>
       <c r="L5" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="s">
         <v>53</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="O5" t="s">
         <v>51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="Q5" t="s">
         <v>54</v>
@@ -2339,741 +2381,741 @@
         <v>55</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>56</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>57</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>58</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
         <v>59</v>
       </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
       <c r="H6" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="I6" t="s">
         <v>60</v>
       </c>
       <c r="J6" t="n">
-        <v>4.05</v>
+        <v>3.97</v>
       </c>
       <c r="K6" t="s">
         <v>61</v>
       </c>
       <c r="L6" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="M6" t="s">
         <v>62</v>
       </c>
       <c r="N6" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="s">
         <v>60</v>
       </c>
       <c r="P6" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" t="s">
         <v>65</v>
       </c>
-      <c r="E7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" t="n">
-        <v>4.54</v>
+        <v>3.72</v>
       </c>
       <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O7" t="s">
         <v>69</v>
       </c>
-      <c r="L7" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="M7" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O7" t="s">
-        <v>68</v>
-      </c>
       <c r="P7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Q7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H8" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J8" t="n">
-        <v>7.04</v>
+        <v>3.93</v>
       </c>
       <c r="K8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L8" t="n">
-        <v>4.16</v>
+        <v>3.89</v>
       </c>
       <c r="M8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P8" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="Q8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H9" t="n">
-        <v>1.96</v>
+        <v>1.37</v>
       </c>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J9" t="n">
-        <v>10.38</v>
+        <v>8.6</v>
       </c>
       <c r="K9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L9" t="n">
-        <v>9.11</v>
+        <v>3</v>
       </c>
       <c r="M9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N9" t="n">
-        <v>1.96</v>
+        <v>1.37</v>
       </c>
       <c r="O9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J10" t="n">
-        <v>14.88</v>
+        <v>5.89</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>5.88</v>
+        <v>7.53</v>
       </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P10" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H11" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J11" t="n">
-        <v>13.81</v>
+        <v>5.33</v>
       </c>
       <c r="K11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L11" t="n">
-        <v>14.82</v>
+        <v>4.46</v>
       </c>
       <c r="M11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="O11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="P11" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="Q11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H12" t="n">
-        <v>3.21</v>
+        <v>2.71</v>
       </c>
       <c r="I12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J12" t="n">
-        <v>20.67</v>
+        <v>3.51</v>
       </c>
       <c r="K12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L12" t="n">
-        <v>11.01</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>2.71</v>
       </c>
       <c r="O12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H13" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J13" t="n">
-        <v>17.55</v>
+        <v>29.07</v>
       </c>
       <c r="K13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L13" t="n">
-        <v>18.86</v>
+        <v>14.2</v>
       </c>
       <c r="M13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N13" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="P13" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Q13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F14" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H14" t="n">
-        <v>4.25</v>
+        <v>3.31</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J14" t="n">
-        <v>31.43</v>
+        <v>12.18</v>
       </c>
       <c r="K14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L14" t="n">
-        <v>8.81</v>
+        <v>3.44</v>
       </c>
       <c r="M14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N14" t="n">
-        <v>4.25</v>
+        <v>3.31</v>
       </c>
       <c r="O14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Q14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H15" t="n">
-        <v>4.91</v>
+        <v>4.13</v>
       </c>
       <c r="I15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J15" t="n">
-        <v>36.1</v>
+        <v>49.41</v>
       </c>
       <c r="K15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
-        <v>49.44</v>
+        <v>20.75</v>
       </c>
       <c r="M15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N15" t="n">
-        <v>4.91</v>
+        <v>4.13</v>
       </c>
       <c r="O15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P15" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="G16" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="H16" t="n">
-        <v>5.23</v>
+        <v>4.59</v>
       </c>
       <c r="I16" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="J16" t="n">
-        <v>42.28</v>
+        <v>22.67</v>
       </c>
       <c r="K16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L16" t="n">
-        <v>33.43</v>
+        <v>15.08</v>
       </c>
       <c r="M16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N16" t="n">
-        <v>5.23</v>
+        <v>4.59</v>
       </c>
       <c r="O16" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="P16" t="n">
         <v>1.13</v>
       </c>
       <c r="Q16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F17" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="H17" t="n">
-        <v>6.23</v>
+        <v>4.65</v>
       </c>
       <c r="I17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J17" t="n">
-        <v>30.64</v>
+        <v>12.95</v>
       </c>
       <c r="K17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L17" t="n">
-        <v>12.95</v>
+        <v>8.15</v>
       </c>
       <c r="M17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N17" t="n">
-        <v>6.23</v>
+        <v>4.65</v>
       </c>
       <c r="O17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="P17" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Q17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D18" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F18" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G18" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="H18" t="n">
-        <v>6.56</v>
+        <v>4.68</v>
       </c>
       <c r="I18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J18" t="n">
-        <v>32.47</v>
+        <v>14.09</v>
       </c>
       <c r="K18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L18" t="n">
-        <v>9.53</v>
+        <v>8.91</v>
       </c>
       <c r="M18" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="O18" t="s">
         <v>168</v>
       </c>
-      <c r="N18" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="O18" t="s">
-        <v>166</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Q18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" t="s">
         <v>173</v>
       </c>
-      <c r="E19" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19" t="s">
-        <v>172</v>
-      </c>
       <c r="G19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H19" t="n">
-        <v>6.88</v>
+        <v>4.99</v>
       </c>
       <c r="I19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J19" t="n">
-        <v>37.25</v>
+        <v>7.85</v>
       </c>
       <c r="K19" t="s">
+        <v>178</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9.54</v>
+      </c>
+      <c r="M19" t="s">
+        <v>179</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="O19" t="s">
         <v>177</v>
       </c>
-      <c r="L19" t="n">
-        <v>25.44</v>
-      </c>
-      <c r="M19" t="s">
-        <v>178</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="O19" t="s">
-        <v>176</v>
-      </c>
       <c r="P19" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="Q19" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20">
@@ -3081,13 +3123,13 @@
         <v>180</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
         <v>181</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
         <v>182</v>
@@ -3099,31 +3141,31 @@
         <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>6.97</v>
+        <v>5.23</v>
       </c>
       <c r="I20" t="s">
         <v>184</v>
       </c>
       <c r="J20" t="n">
-        <v>50.07</v>
+        <v>49.29</v>
       </c>
       <c r="K20" t="s">
         <v>185</v>
       </c>
       <c r="L20" t="n">
-        <v>23.13</v>
+        <v>18.16</v>
       </c>
       <c r="M20" t="s">
         <v>186</v>
       </c>
       <c r="N20" t="n">
-        <v>6.97</v>
+        <v>5.23</v>
       </c>
       <c r="O20" t="s">
         <v>184</v>
       </c>
       <c r="P20" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="s">
         <v>187</v>
@@ -3134,3179 +3176,3179 @@
         <v>188</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>189</v>
       </c>
       <c r="D21" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F21" t="s">
         <v>189</v>
       </c>
       <c r="G21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H21" t="n">
-        <v>7.31</v>
+        <v>5.45</v>
       </c>
       <c r="I21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J21" t="n">
-        <v>32.53</v>
+        <v>38.51</v>
       </c>
       <c r="K21" t="s">
+        <v>194</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="M21" t="s">
+        <v>195</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="O21" t="s">
         <v>193</v>
       </c>
-      <c r="L21" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="M21" t="s">
-        <v>194</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="O21" t="s">
-        <v>192</v>
-      </c>
       <c r="P21" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Q21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" t="s">
         <v>198</v>
       </c>
-      <c r="F22" t="s">
-        <v>129</v>
-      </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>8.81</v>
+        <v>6.62</v>
       </c>
       <c r="I22" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="J22" t="n">
-        <v>34.09</v>
+        <v>29.3</v>
       </c>
       <c r="K22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L22" t="n">
-        <v>13.11</v>
+        <v>28.47</v>
       </c>
       <c r="M22" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N22" t="n">
-        <v>8.81</v>
+        <v>6.62</v>
       </c>
       <c r="O22" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="P22" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="Q22" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="E23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F23" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H23" t="n">
-        <v>11.31</v>
+        <v>6.79</v>
       </c>
       <c r="I23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J23" t="n">
-        <v>41.62</v>
+        <v>13.53</v>
       </c>
       <c r="K23" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="L23" t="n">
-        <v>39.27</v>
+        <v>7</v>
       </c>
       <c r="M23" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N23" t="n">
-        <v>11.31</v>
+        <v>6.79</v>
       </c>
       <c r="O23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="P23" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D24" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E24" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F24" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G24" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H24" t="n">
-        <v>11.54</v>
+        <v>7.82</v>
       </c>
       <c r="I24" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J24" t="n">
-        <v>68.1</v>
+        <v>45.61</v>
       </c>
       <c r="K24" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L24" t="n">
-        <v>61.58</v>
+        <v>36.28</v>
       </c>
       <c r="M24" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N24" t="n">
-        <v>11.54</v>
+        <v>7.82</v>
       </c>
       <c r="O24" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q24" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C25" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="G25" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H25" t="n">
-        <v>11.67</v>
+        <v>8.15</v>
       </c>
       <c r="I25" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="J25" t="n">
-        <v>58.39</v>
+        <v>7.95</v>
       </c>
       <c r="K25" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L25" t="n">
-        <v>41.03</v>
+        <v>7.51</v>
       </c>
       <c r="M25" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N25" t="n">
-        <v>11.67</v>
+        <v>8.15</v>
       </c>
       <c r="O25" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="P25" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="Q25" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" t="s">
         <v>231</v>
       </c>
-      <c r="E26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" t="s">
-        <v>230</v>
-      </c>
       <c r="G26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H26" t="n">
-        <v>11.89</v>
+        <v>13.25</v>
       </c>
       <c r="I26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J26" t="n">
-        <v>71.23</v>
+        <v>85.72</v>
       </c>
       <c r="K26" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L26" t="n">
-        <v>50.79</v>
+        <v>61.48</v>
       </c>
       <c r="M26" t="s">
+        <v>237</v>
+      </c>
+      <c r="N26" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="O26" t="s">
         <v>235</v>
       </c>
-      <c r="N26" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="O26" t="s">
-        <v>233</v>
-      </c>
       <c r="P26" t="n">
-        <v>1.21</v>
+        <v>3.33</v>
       </c>
       <c r="Q26" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D27" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E27" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F27" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G27" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H27" t="n">
-        <v>11.95</v>
+        <v>13.9</v>
       </c>
       <c r="I27" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J27" t="n">
-        <v>54.58</v>
+        <v>66.9</v>
       </c>
       <c r="K27" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L27" t="n">
-        <v>17.46</v>
+        <v>59.96</v>
       </c>
       <c r="M27" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N27" t="n">
-        <v>11.95</v>
+        <v>13.9</v>
       </c>
       <c r="O27" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P27" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Q27" t="s">
-        <v>23</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D28" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E28" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="G28" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H28" t="n">
-        <v>12.93</v>
+        <v>14.13</v>
       </c>
       <c r="I28" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J28" t="n">
-        <v>43.58</v>
+        <v>67.19</v>
       </c>
       <c r="K28" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L28" t="n">
-        <v>39.6</v>
+        <v>54.79</v>
       </c>
       <c r="M28" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N28" t="n">
-        <v>12.93</v>
+        <v>14.13</v>
       </c>
       <c r="O28" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="P28" t="n">
-        <v>1.17</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
-        <v>253</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="F29" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="H29" t="n">
-        <v>13.53</v>
+        <v>15.53</v>
       </c>
       <c r="I29" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J29" t="n">
-        <v>76.14</v>
+        <v>49.36</v>
       </c>
       <c r="K29" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L29" t="n">
-        <v>65.11</v>
+        <v>78.54</v>
       </c>
       <c r="M29" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N29" t="n">
-        <v>13.53</v>
+        <v>15.53</v>
       </c>
       <c r="O29" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P29" t="n">
-        <v>1.42</v>
+        <v>2.85</v>
       </c>
       <c r="Q29" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" t="s">
+        <v>265</v>
+      </c>
+      <c r="E30" t="s">
         <v>257</v>
       </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D30" t="s">
-        <v>212</v>
-      </c>
-      <c r="E30" t="s">
-        <v>259</v>
-      </c>
       <c r="F30" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="G30" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="H30" t="n">
-        <v>14.06</v>
+        <v>16.93</v>
       </c>
       <c r="I30" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="J30" t="n">
-        <v>67.45</v>
+        <v>94.86</v>
       </c>
       <c r="K30" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="L30" t="n">
-        <v>82.06</v>
+        <v>79.85</v>
       </c>
       <c r="M30" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N30" t="n">
-        <v>14.06</v>
+        <v>16.93</v>
       </c>
       <c r="O30" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="Q30" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>266</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="F31" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="G31" t="s">
+        <v>273</v>
+      </c>
+      <c r="H31" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="I31" t="s">
         <v>267</v>
       </c>
-      <c r="H31" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="I31" t="s">
-        <v>268</v>
-      </c>
       <c r="J31" t="n">
-        <v>94.17</v>
+        <v>49.14</v>
       </c>
       <c r="K31" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L31" t="n">
-        <v>72.34</v>
+        <v>24.08</v>
       </c>
       <c r="M31" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="N31" t="n">
-        <v>14.18</v>
+        <v>16.93</v>
       </c>
       <c r="O31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P31" t="n">
-        <v>1.23</v>
+        <v>2.58</v>
       </c>
       <c r="Q31" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E32" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="F32" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="G32" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H32" t="n">
-        <v>14.49</v>
+        <v>16.92</v>
       </c>
       <c r="I32" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J32" t="n">
-        <v>37.96</v>
+        <v>48.44</v>
       </c>
       <c r="K32" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="L32" t="n">
-        <v>77.08</v>
+        <v>19.96</v>
       </c>
       <c r="M32" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N32" t="n">
-        <v>14.49</v>
+        <v>16.92</v>
       </c>
       <c r="O32" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P32" t="n">
-        <v>1.45</v>
+        <v>2.96</v>
       </c>
       <c r="Q32" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>286</v>
       </c>
       <c r="C33" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D33" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>238</v>
+        <v>140</v>
       </c>
       <c r="F33" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G33" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H33" t="n">
-        <v>15.4</v>
+        <v>18.63</v>
       </c>
       <c r="I33" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="J33" t="n">
-        <v>47.56</v>
+        <v>25.55</v>
       </c>
       <c r="K33" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="L33" t="n">
-        <v>55.94</v>
+        <v>50.69</v>
       </c>
       <c r="M33" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="N33" t="n">
-        <v>15.4</v>
+        <v>18.63</v>
       </c>
       <c r="O33" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="Q33" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C34" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D34" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E34" t="s">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="F34" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="G34" t="s">
-        <v>211</v>
+        <v>297</v>
       </c>
       <c r="H34" t="n">
-        <v>15.41</v>
+        <v>21.27</v>
       </c>
       <c r="I34" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="J34" t="n">
-        <v>74.84</v>
+        <v>92.17</v>
       </c>
       <c r="K34" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="L34" t="n">
-        <v>106.22</v>
+        <v>51.13</v>
       </c>
       <c r="M34" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N34" t="n">
-        <v>15.41</v>
+        <v>21.27</v>
       </c>
       <c r="O34" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="P34" t="n">
-        <v>11.52</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="D35" t="s">
-        <v>253</v>
+        <v>304</v>
       </c>
       <c r="E35" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="F35" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G35" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="H35" t="n">
-        <v>15.37</v>
+        <v>23.31</v>
       </c>
       <c r="I35" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="J35" t="n">
-        <v>75.44</v>
+        <v>100.96</v>
       </c>
       <c r="K35" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="L35" t="n">
-        <v>87.92</v>
+        <v>96.6</v>
       </c>
       <c r="M35" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="N35" t="n">
-        <v>15.37</v>
+        <v>23.31</v>
       </c>
       <c r="O35" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="P35" t="n">
-        <v>3.69</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>311</v>
       </c>
       <c r="C36" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="D36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E36" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="F36" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="G36" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="H36" t="n">
-        <v>15.28</v>
+        <v>24.48</v>
       </c>
       <c r="I36" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="J36" t="n">
-        <v>72.97</v>
+        <v>86.56</v>
       </c>
       <c r="K36" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="L36" t="n">
-        <v>92.76</v>
+        <v>16.32</v>
       </c>
       <c r="M36" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="N36" t="n">
-        <v>15.28</v>
+        <v>24.48</v>
       </c>
       <c r="O36" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="P36" t="n">
-        <v>4.46</v>
+        <v>1.72</v>
       </c>
       <c r="Q36" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="D37" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="F37" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="G37" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="H37" t="n">
-        <v>15.5</v>
+        <v>24.79</v>
       </c>
       <c r="I37" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="J37" t="n">
-        <v>70.66</v>
+        <v>66.09</v>
       </c>
       <c r="K37" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="L37" t="n">
-        <v>96.1</v>
+        <v>53.15</v>
       </c>
       <c r="M37" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="N37" t="n">
-        <v>15.5</v>
+        <v>24.79</v>
       </c>
       <c r="O37" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="P37" t="n">
-        <v>5.64</v>
+        <v>1.44</v>
       </c>
       <c r="Q37" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>286</v>
       </c>
       <c r="C38" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D38" t="s">
-        <v>253</v>
+        <v>328</v>
       </c>
       <c r="E38" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F38" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G38" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="H38" t="n">
-        <v>15.51</v>
+        <v>25.3</v>
       </c>
       <c r="I38" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="J38" t="n">
-        <v>76.63</v>
+        <v>70.83</v>
       </c>
       <c r="K38" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="L38" t="n">
-        <v>103.75</v>
+        <v>16.3</v>
       </c>
       <c r="M38" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="N38" t="n">
-        <v>15.51</v>
+        <v>25.3</v>
       </c>
       <c r="O38" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="P38" t="n">
-        <v>8.17</v>
+        <v>2.09</v>
       </c>
       <c r="Q38" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="D39" t="s">
-        <v>231</v>
+        <v>304</v>
       </c>
       <c r="E39" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="F39" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="G39" t="s">
-        <v>172</v>
+        <v>335</v>
       </c>
       <c r="H39" t="n">
-        <v>15.62</v>
+        <v>25.39</v>
       </c>
       <c r="I39" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="J39" t="n">
-        <v>72.78</v>
+        <v>96.1</v>
       </c>
       <c r="K39" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="L39" t="n">
-        <v>101.77</v>
+        <v>89.71</v>
       </c>
       <c r="M39" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="N39" t="n">
-        <v>15.62</v>
+        <v>25.39</v>
       </c>
       <c r="O39" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="P39" t="n">
-        <v>6.92</v>
+        <v>2.01</v>
       </c>
       <c r="Q39" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="D40" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E40" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F40" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="G40" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="H40" t="n">
-        <v>15.64</v>
+        <v>25.56</v>
       </c>
       <c r="I40" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="J40" t="n">
-        <v>75.7</v>
+        <v>123.81</v>
       </c>
       <c r="K40" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="L40" t="n">
-        <v>103.51</v>
+        <v>115.72</v>
       </c>
       <c r="M40" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="N40" t="n">
-        <v>15.64</v>
+        <v>25.56</v>
       </c>
       <c r="O40" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="P40" t="n">
-        <v>5.4</v>
+        <v>4.71</v>
       </c>
       <c r="Q40" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="D41" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="E41" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="F41" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="G41" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="H41" t="n">
-        <v>15.82</v>
+        <v>36.33</v>
       </c>
       <c r="I41" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="J41" t="n">
-        <v>76.15</v>
+        <v>110.92</v>
       </c>
       <c r="K41" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="L41" t="n">
-        <v>104.99</v>
+        <v>91.45</v>
       </c>
       <c r="M41" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="N41" t="n">
-        <v>15.82</v>
+        <v>36.33</v>
       </c>
       <c r="O41" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="P41" t="n">
-        <v>8.06</v>
+        <v>2.34</v>
       </c>
       <c r="Q41" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s">
-        <v>220</v>
+        <v>355</v>
       </c>
       <c r="C42" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="D42" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="E42" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="F42" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="G42" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="H42" t="n">
-        <v>16.77</v>
+        <v>42.24</v>
       </c>
       <c r="I42" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="J42" t="n">
-        <v>75.51</v>
+        <v>112.22</v>
       </c>
       <c r="K42" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="L42" t="n">
-        <v>105.66</v>
+        <v>70.55</v>
       </c>
       <c r="M42" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="N42" t="n">
-        <v>16.77</v>
+        <v>42.24</v>
       </c>
       <c r="O42" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="P42" t="n">
-        <v>11.21</v>
+        <v>11.08</v>
       </c>
       <c r="Q42" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="D43" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E43" t="s">
-        <v>231</v>
+        <v>342</v>
       </c>
       <c r="F43" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="G43" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="H43" t="n">
-        <v>18.02</v>
+        <v>45.61</v>
       </c>
       <c r="I43" t="s">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="J43" t="n">
-        <v>46.5</v>
+        <v>119.87</v>
       </c>
       <c r="K43" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="L43" t="n">
-        <v>70.07</v>
+        <v>114.58</v>
       </c>
       <c r="M43" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="N43" t="n">
-        <v>18.02</v>
+        <v>45.61</v>
       </c>
       <c r="O43" t="s">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="P43" t="n">
-        <v>1.79</v>
+        <v>7.66</v>
       </c>
       <c r="Q43" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="C44" t="s">
-        <v>355</v>
+        <v>216</v>
       </c>
       <c r="D44" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="E44" t="s">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="F44" t="s">
-        <v>355</v>
+        <v>216</v>
       </c>
       <c r="G44" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="H44" t="n">
-        <v>19.21</v>
+        <v>44.56</v>
       </c>
       <c r="I44" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="J44" t="n">
-        <v>64.79</v>
+        <v>113.94</v>
       </c>
       <c r="K44" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="L44" t="n">
-        <v>72.12</v>
+        <v>72.24</v>
       </c>
       <c r="M44" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="N44" t="n">
-        <v>19.21</v>
+        <v>44.56</v>
       </c>
       <c r="O44" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="P44" t="n">
-        <v>1.35</v>
+        <v>11.74</v>
       </c>
       <c r="Q44" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>362</v>
+        <v>278</v>
       </c>
       <c r="D45" t="s">
-        <v>213</v>
+        <v>341</v>
       </c>
       <c r="E45" t="s">
-        <v>213</v>
+        <v>342</v>
       </c>
       <c r="F45" t="s">
-        <v>362</v>
+        <v>278</v>
       </c>
       <c r="G45" t="s">
-        <v>363</v>
+        <v>97</v>
       </c>
       <c r="H45" t="n">
-        <v>21.06</v>
+        <v>46.87</v>
       </c>
       <c r="I45" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J45" t="n">
-        <v>60.96</v>
+        <v>119.07</v>
       </c>
       <c r="K45" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="L45" t="n">
-        <v>61.7</v>
+        <v>108.51</v>
       </c>
       <c r="M45" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="N45" t="n">
-        <v>21.06</v>
+        <v>46.87</v>
       </c>
       <c r="O45" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="P45" t="n">
-        <v>1.56</v>
+        <v>7.52</v>
       </c>
       <c r="Q45" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>369</v>
+        <v>242</v>
       </c>
       <c r="D46" t="s">
-        <v>231</v>
+        <v>342</v>
       </c>
       <c r="E46" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="F46" t="s">
-        <v>369</v>
+        <v>242</v>
       </c>
       <c r="G46" t="s">
-        <v>275</v>
+        <v>379</v>
       </c>
       <c r="H46" t="n">
-        <v>22.28</v>
+        <v>59.84</v>
       </c>
       <c r="I46" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="J46" t="n">
-        <v>72.76</v>
+        <v>108.25</v>
       </c>
       <c r="K46" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L46" t="n">
-        <v>77.27</v>
+        <v>105.86</v>
       </c>
       <c r="M46" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="N46" t="n">
-        <v>22.28</v>
+        <v>59.84</v>
       </c>
       <c r="O46" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="P46" t="n">
-        <v>1.45</v>
+        <v>5.06</v>
       </c>
       <c r="Q46" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="D47" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="E47" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="G47" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H47" t="n">
-        <v>23.07</v>
+        <v>61.8</v>
       </c>
       <c r="I47" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="J47" t="n">
-        <v>66.89</v>
+        <v>108.43</v>
       </c>
       <c r="K47" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="L47" t="n">
-        <v>67.98</v>
+        <v>78.03</v>
       </c>
       <c r="M47" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="N47" t="n">
-        <v>23.07</v>
+        <v>61.8</v>
       </c>
       <c r="O47" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="P47" t="n">
-        <v>1.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q47" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>382</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="E48" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="F48" t="s">
-        <v>382</v>
+        <v>233</v>
       </c>
       <c r="G48" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="H48" t="n">
-        <v>24.26</v>
+        <v>62.62</v>
       </c>
       <c r="I48" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="J48" t="n">
-        <v>68.01</v>
+        <v>112.8</v>
       </c>
       <c r="K48" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="L48" t="n">
-        <v>102.28</v>
+        <v>94.48</v>
       </c>
       <c r="M48" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="N48" t="n">
-        <v>24.26</v>
+        <v>62.62</v>
       </c>
       <c r="O48" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="P48" t="n">
-        <v>18.04</v>
+        <v>3.48</v>
       </c>
       <c r="Q48" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>389</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>213</v>
+        <v>342</v>
       </c>
       <c r="E49" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="F49" t="s">
-        <v>389</v>
+        <v>233</v>
       </c>
       <c r="G49" t="s">
-        <v>349</v>
+        <v>398</v>
       </c>
       <c r="H49" t="n">
-        <v>27.32</v>
+        <v>61.95</v>
       </c>
       <c r="I49" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="J49" t="n">
-        <v>62.53</v>
+        <v>116.36</v>
       </c>
       <c r="K49" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="L49" t="n">
-        <v>65.53</v>
+        <v>110.34</v>
       </c>
       <c r="M49" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="N49" t="n">
-        <v>27.32</v>
+        <v>61.95</v>
       </c>
       <c r="O49" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>3.11</v>
       </c>
       <c r="Q49" t="s">
-        <v>353</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>355</v>
       </c>
       <c r="C50" t="s">
-        <v>394</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>231</v>
+        <v>342</v>
       </c>
       <c r="E50" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="F50" t="s">
-        <v>394</v>
+        <v>233</v>
       </c>
       <c r="G50" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="H50" t="n">
-        <v>28.22</v>
+        <v>62.48</v>
       </c>
       <c r="I50" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="J50" t="n">
-        <v>72.58</v>
+        <v>115.4</v>
       </c>
       <c r="K50" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L50" t="n">
-        <v>106.18</v>
+        <v>91.85</v>
       </c>
       <c r="M50" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="N50" t="n">
-        <v>28.22</v>
+        <v>62.48</v>
       </c>
       <c r="O50" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="P50" t="n">
-        <v>18.19</v>
+        <v>19.66</v>
       </c>
       <c r="Q50" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>385</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="D51" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="E51" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F51" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="G51" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="H51" t="n">
-        <v>31.07</v>
+        <v>64.07</v>
       </c>
       <c r="I51" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="J51" t="n">
-        <v>76.07</v>
+        <v>114.35</v>
       </c>
       <c r="K51" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="L51" t="n">
-        <v>105.11</v>
+        <v>116.68</v>
       </c>
       <c r="M51" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="N51" t="n">
-        <v>31.07</v>
+        <v>64.07</v>
       </c>
       <c r="O51" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="P51" t="n">
-        <v>5.38</v>
+        <v>6.07</v>
       </c>
       <c r="Q51" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s">
-        <v>289</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="D52" t="s">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="E52" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="F52" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="G52" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="H52" t="n">
-        <v>34.37</v>
+        <v>63.39</v>
       </c>
       <c r="I52" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="J52" t="n">
-        <v>67.29</v>
+        <v>94.5</v>
       </c>
       <c r="K52" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L52" t="n">
-        <v>84.72</v>
+        <v>109.63</v>
       </c>
       <c r="M52" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="N52" t="n">
-        <v>34.37</v>
+        <v>63.39</v>
       </c>
       <c r="O52" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="Q52" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
-        <v>213</v>
+        <v>341</v>
       </c>
       <c r="E53" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="G53" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="H53" t="n">
-        <v>36.04</v>
+        <v>61.93</v>
       </c>
       <c r="I53" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="J53" t="n">
-        <v>63.04</v>
+        <v>125</v>
       </c>
       <c r="K53" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="L53" t="n">
-        <v>93.81</v>
+        <v>114.51</v>
       </c>
       <c r="M53" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="N53" t="n">
-        <v>36.04</v>
+        <v>61.93</v>
       </c>
       <c r="O53" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>9.59</v>
       </c>
       <c r="Q53" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>213</v>
+        <v>341</v>
       </c>
       <c r="E54" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F54" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="G54" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="H54" t="n">
-        <v>35.58</v>
+        <v>66.48</v>
       </c>
       <c r="I54" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="J54" t="n">
-        <v>62.91</v>
+        <v>120.27</v>
       </c>
       <c r="K54" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="L54" t="n">
-        <v>103.83</v>
+        <v>112.25</v>
       </c>
       <c r="M54" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="N54" t="n">
-        <v>35.58</v>
+        <v>66.48</v>
       </c>
       <c r="O54" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="P54" t="n">
-        <v>11.08</v>
+        <v>3.83</v>
       </c>
       <c r="Q54" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s">
-        <v>289</v>
+        <v>434</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>328</v>
       </c>
       <c r="D55" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E55" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>328</v>
       </c>
       <c r="G55" t="s">
-        <v>316</v>
+        <v>86</v>
       </c>
       <c r="H55" t="n">
-        <v>36.1</v>
+        <v>69.75</v>
       </c>
       <c r="I55" t="s">
-        <v>141</v>
+        <v>435</v>
       </c>
       <c r="J55" t="n">
-        <v>71.07</v>
+        <v>119.96</v>
       </c>
       <c r="K55" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="L55" t="n">
-        <v>101.7</v>
+        <v>104.53</v>
       </c>
       <c r="M55" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="N55" t="n">
-        <v>36.1</v>
+        <v>69.75</v>
       </c>
       <c r="O55" t="s">
-        <v>141</v>
+        <v>435</v>
       </c>
       <c r="P55" t="n">
-        <v>8.23</v>
+        <v>8.61</v>
       </c>
       <c r="Q55" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>286</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="D56" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E56" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="F56" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G56" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="H56" t="n">
-        <v>36.49</v>
+        <v>71.26</v>
       </c>
       <c r="I56" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="J56" t="n">
-        <v>70.02</v>
+        <v>120.43</v>
       </c>
       <c r="K56" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="L56" t="n">
-        <v>100.49</v>
+        <v>117.88</v>
       </c>
       <c r="M56" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="N56" t="n">
-        <v>36.49</v>
+        <v>71.26</v>
       </c>
       <c r="O56" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="P56" t="n">
-        <v>5.83</v>
+        <v>9.96</v>
       </c>
       <c r="Q56" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
+        <v>385</v>
       </c>
       <c r="C57" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="D57" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E57" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F57" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G57" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="H57" t="n">
-        <v>36.85</v>
+        <v>72.83</v>
       </c>
       <c r="I57" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="J57" t="n">
-        <v>72.12</v>
+        <v>121.58</v>
       </c>
       <c r="K57" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="L57" t="n">
-        <v>95.42</v>
+        <v>116.51</v>
       </c>
       <c r="M57" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="N57" t="n">
-        <v>36.85</v>
+        <v>72.83</v>
       </c>
       <c r="O57" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="P57" t="n">
-        <v>2.94</v>
+        <v>7.42</v>
       </c>
       <c r="Q57" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="D58" t="s">
-        <v>213</v>
+        <v>341</v>
       </c>
       <c r="E58" t="s">
-        <v>266</v>
+        <v>341</v>
       </c>
       <c r="F58" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G58" t="s">
-        <v>440</v>
+        <v>256</v>
       </c>
       <c r="H58" t="n">
-        <v>37.17</v>
+        <v>69.66</v>
       </c>
       <c r="I58" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="J58" t="n">
-        <v>62.37</v>
+        <v>125.65</v>
       </c>
       <c r="K58" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="L58" t="n">
-        <v>94.5</v>
+        <v>127.47</v>
       </c>
       <c r="M58" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="N58" t="n">
-        <v>37.17</v>
+        <v>69.66</v>
       </c>
       <c r="O58" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="P58" t="n">
-        <v>7.67</v>
+        <v>15.68</v>
       </c>
       <c r="Q58" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>355</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="D59" t="s">
-        <v>231</v>
+        <v>342</v>
       </c>
       <c r="E59" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="F59" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G59" t="s">
-        <v>111</v>
+        <v>279</v>
       </c>
       <c r="H59" t="n">
-        <v>37.58</v>
+        <v>72.87</v>
       </c>
       <c r="I59" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="J59" t="n">
-        <v>72.53</v>
+        <v>116.32</v>
       </c>
       <c r="K59" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="L59" t="n">
-        <v>106.77</v>
+        <v>87.76</v>
       </c>
       <c r="M59" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="N59" t="n">
-        <v>37.58</v>
+        <v>72.87</v>
       </c>
       <c r="O59" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="P59" t="n">
-        <v>10.95</v>
+        <v>20.03</v>
       </c>
       <c r="Q59" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="D60" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E60" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F60" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="G60" t="s">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="H60" t="n">
-        <v>39.07</v>
+        <v>76.18</v>
       </c>
       <c r="I60" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="J60" t="n">
-        <v>73.43</v>
+        <v>121.15</v>
       </c>
       <c r="K60" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="L60" t="n">
-        <v>103.95</v>
+        <v>103.23</v>
       </c>
       <c r="M60" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="N60" t="n">
-        <v>39.07</v>
+        <v>76.18</v>
       </c>
       <c r="O60" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="P60" t="n">
-        <v>10.37</v>
+        <v>7.27</v>
       </c>
       <c r="Q60" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>469</v>
       </c>
       <c r="C61" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="D61" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E61" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="F61" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="G61" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="H61" t="n">
-        <v>37.83</v>
+        <v>77.16</v>
       </c>
       <c r="I61" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="J61" t="n">
-        <v>70.87</v>
+        <v>124.72</v>
       </c>
       <c r="K61" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="L61" t="n">
-        <v>93.61</v>
+        <v>114.42</v>
       </c>
       <c r="M61" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="N61" t="n">
-        <v>37.83</v>
+        <v>77.16</v>
       </c>
       <c r="O61" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="P61" t="n">
-        <v>4.48</v>
+        <v>18.88</v>
       </c>
       <c r="Q61" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s">
-        <v>439</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="D62" t="s">
-        <v>213</v>
+        <v>341</v>
       </c>
       <c r="E62" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F62" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="G62" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="H62" t="n">
-        <v>38.09</v>
+        <v>74.33</v>
       </c>
       <c r="I62" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="J62" t="n">
-        <v>63.13</v>
+        <v>123.96</v>
       </c>
       <c r="K62" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="L62" t="n">
-        <v>96.48</v>
+        <v>110.15</v>
       </c>
       <c r="M62" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="N62" t="n">
-        <v>38.09</v>
+        <v>74.33</v>
       </c>
       <c r="O62" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="P62" t="n">
-        <v>6.99</v>
+        <v>13.2</v>
       </c>
       <c r="Q62" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="D63" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="E63" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="F63" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="G63" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="H63" t="n">
-        <v>39.98</v>
+        <v>75.27</v>
       </c>
       <c r="I63" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="J63" t="n">
-        <v>73.35</v>
+        <v>90.98</v>
       </c>
       <c r="K63" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="L63" t="n">
-        <v>102.38</v>
+        <v>117.94</v>
       </c>
       <c r="M63" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="N63" t="n">
-        <v>39.98</v>
+        <v>75.27</v>
       </c>
       <c r="O63" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="P63" t="n">
-        <v>3.24</v>
+        <v>8.77</v>
       </c>
       <c r="Q63" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>286</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E64" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="F64" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="G64" t="s">
-        <v>474</v>
+        <v>379</v>
       </c>
       <c r="H64" t="n">
-        <v>39.54</v>
+        <v>79.65</v>
       </c>
       <c r="I64" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="J64" t="n">
-        <v>74.99</v>
+        <v>122.09</v>
       </c>
       <c r="K64" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="L64" t="n">
-        <v>102.1</v>
+        <v>118.02</v>
       </c>
       <c r="M64" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="N64" t="n">
-        <v>39.54</v>
+        <v>79.65</v>
       </c>
       <c r="O64" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="P64" t="n">
-        <v>4.57</v>
+        <v>5.05</v>
       </c>
       <c r="Q64" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>311</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="D65" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E65" t="s">
-        <v>308</v>
+        <v>493</v>
       </c>
       <c r="F65" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="H65" t="n">
-        <v>41.51</v>
+        <v>83.42</v>
       </c>
       <c r="I65" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="J65" t="n">
-        <v>73.71</v>
+        <v>120.85</v>
       </c>
       <c r="K65" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="L65" t="n">
-        <v>105.25</v>
+        <v>17.47</v>
       </c>
       <c r="M65" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="N65" t="n">
-        <v>41.51</v>
+        <v>83.42</v>
       </c>
       <c r="O65" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="P65" t="n">
-        <v>17.77</v>
+        <v>25.92</v>
       </c>
       <c r="Q65" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s">
-        <v>439</v>
+        <v>148</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="D66" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="E66" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F66" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="G66" t="s">
-        <v>155</v>
+        <v>499</v>
       </c>
       <c r="H66" t="n">
-        <v>41.98</v>
+        <v>82.54</v>
       </c>
       <c r="I66" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="J66" t="n">
-        <v>67.52</v>
+        <v>123.96</v>
       </c>
       <c r="K66" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="L66" t="n">
-        <v>104.71</v>
+        <v>107.89</v>
       </c>
       <c r="M66" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="N66" t="n">
-        <v>41.98</v>
+        <v>82.54</v>
       </c>
       <c r="O66" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="P66" t="n">
-        <v>13.06</v>
+        <v>3.74</v>
       </c>
       <c r="Q66" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s">
-        <v>220</v>
+        <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="D67" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E67" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="F67" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="G67" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="H67" t="n">
-        <v>42.5</v>
+        <v>80.1</v>
       </c>
       <c r="I67" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="J67" t="n">
-        <v>76.42</v>
+        <v>124.1</v>
       </c>
       <c r="K67" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="L67" t="n">
-        <v>102.72</v>
+        <v>107.49</v>
       </c>
       <c r="M67" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="N67" t="n">
-        <v>42.5</v>
+        <v>80.1</v>
       </c>
       <c r="O67" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="P67" t="n">
-        <v>5.56</v>
+        <v>10.56</v>
       </c>
       <c r="Q67" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s">
-        <v>496</v>
+        <v>295</v>
       </c>
       <c r="C68" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="D68" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E68" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="F68" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="G68" t="s">
-        <v>334</v>
+        <v>510</v>
       </c>
       <c r="H68" t="n">
-        <v>44.04</v>
+        <v>85.72</v>
       </c>
       <c r="I68" t="s">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="J68" t="n">
-        <v>75.49</v>
+        <v>120.76</v>
       </c>
       <c r="K68" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="L68" t="n">
-        <v>106.76</v>
+        <v>107.55</v>
       </c>
       <c r="M68" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="N68" t="n">
-        <v>44.04</v>
+        <v>85.72</v>
       </c>
       <c r="O68" t="s">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="P68" t="n">
-        <v>15.95</v>
+        <v>11.23</v>
       </c>
       <c r="Q68" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s">
-        <v>439</v>
+        <v>46</v>
       </c>
       <c r="C69" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D69" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="E69" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="F69" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="G69" t="s">
-        <v>502</v>
+        <v>191</v>
       </c>
       <c r="H69" t="n">
-        <v>43.33</v>
+        <v>95.18</v>
       </c>
       <c r="I69" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="J69" t="n">
-        <v>68.11</v>
+        <v>123.15</v>
       </c>
       <c r="K69" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="L69" t="n">
-        <v>109.59</v>
+        <v>110.64</v>
       </c>
       <c r="M69" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="N69" t="n">
-        <v>43.33</v>
+        <v>95.18</v>
       </c>
       <c r="O69" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="P69" t="n">
-        <v>14.62</v>
+        <v>27.24</v>
       </c>
       <c r="Q69" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s">
-        <v>322</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E70" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="F70" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="G70" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H70" t="n">
-        <v>44.25</v>
+        <v>89.5</v>
       </c>
       <c r="I70" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="J70" t="n">
-        <v>76.57</v>
+        <v>123.19</v>
       </c>
       <c r="K70" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="L70" t="n">
-        <v>108.64</v>
+        <v>109.85</v>
       </c>
       <c r="M70" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="N70" t="n">
-        <v>44.25</v>
+        <v>89.5</v>
       </c>
       <c r="O70" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="P70" t="n">
-        <v>15.47</v>
+        <v>13.5</v>
       </c>
       <c r="Q70" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B71" t="s">
-        <v>322</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="E71" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="F71" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="G71" t="s">
-        <v>154</v>
+        <v>525</v>
       </c>
       <c r="H71" t="n">
-        <v>44.3</v>
+        <v>87.66</v>
       </c>
       <c r="I71" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="J71" t="n">
-        <v>73.46</v>
+        <v>119.85</v>
       </c>
       <c r="K71" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="L71" t="n">
-        <v>109.9</v>
+        <v>109.44</v>
       </c>
       <c r="M71" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="N71" t="n">
-        <v>44.3</v>
+        <v>87.66</v>
       </c>
       <c r="O71" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="P71" t="n">
-        <v>30</v>
+        <v>4.87</v>
       </c>
       <c r="Q71" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="C72" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D72" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>493</v>
       </c>
       <c r="F72" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="G72" t="s">
-        <v>518</v>
+        <v>199</v>
       </c>
       <c r="H72" t="n">
-        <v>43.34</v>
+        <v>91.35</v>
       </c>
       <c r="I72" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="J72" t="n">
-        <v>76.7</v>
+        <v>122.19</v>
       </c>
       <c r="K72" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="L72" t="n">
-        <v>104.95</v>
+        <v>17.65</v>
       </c>
       <c r="M72" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="N72" t="n">
-        <v>43.34</v>
+        <v>91.35</v>
       </c>
       <c r="O72" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="P72" t="n">
-        <v>10.27</v>
+        <v>28.25</v>
       </c>
       <c r="Q72" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="B73" t="s">
-        <v>229</v>
+        <v>536</v>
       </c>
       <c r="C73" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="D73" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E73" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="F73" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="G73" t="s">
-        <v>182</v>
+        <v>537</v>
       </c>
       <c r="H73" t="n">
-        <v>44.96</v>
+        <v>92.85</v>
       </c>
       <c r="I73" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="J73" t="n">
-        <v>75.79</v>
+        <v>124.7</v>
       </c>
       <c r="K73" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="L73" t="n">
-        <v>108.46</v>
+        <v>115.07</v>
       </c>
       <c r="M73" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="N73" t="n">
-        <v>44.96</v>
+        <v>92.85</v>
       </c>
       <c r="O73" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="P73" t="n">
-        <v>23.41</v>
+        <v>10.24</v>
       </c>
       <c r="Q73" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="B74" t="s">
-        <v>529</v>
+        <v>434</v>
       </c>
       <c r="C74" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="D74" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E74" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F74" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="G74" t="s">
-        <v>154</v>
+        <v>543</v>
       </c>
       <c r="H74" t="n">
-        <v>44.84</v>
+        <v>94.29</v>
       </c>
       <c r="I74" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="J74" t="n">
-        <v>75.99</v>
+        <v>125.47</v>
       </c>
       <c r="K74" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="L74" t="n">
-        <v>108.66</v>
+        <v>118.06</v>
       </c>
       <c r="M74" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="N74" t="n">
-        <v>44.84</v>
+        <v>94.29</v>
       </c>
       <c r="O74" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="P74" t="n">
-        <v>29.97</v>
+        <v>14.76</v>
       </c>
       <c r="Q74" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="B75" t="s">
-        <v>529</v>
+        <v>286</v>
       </c>
       <c r="C75" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="D75" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E75" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F75" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="G75" t="s">
-        <v>369</v>
+        <v>549</v>
       </c>
       <c r="H75" t="n">
-        <v>45.91</v>
+        <v>95.92</v>
       </c>
       <c r="I75" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="J75" t="n">
-        <v>78.01</v>
+        <v>120.81</v>
       </c>
       <c r="K75" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="L75" t="n">
-        <v>110.71</v>
+        <v>120.16</v>
       </c>
       <c r="M75" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="N75" t="n">
-        <v>45.91</v>
+        <v>95.92</v>
       </c>
       <c r="O75" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="P75" t="n">
-        <v>22.2</v>
+        <v>7.48</v>
       </c>
       <c r="Q75" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="B76" t="s">
-        <v>439</v>
+        <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="D76" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E76" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F76" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="G76" t="s">
-        <v>389</v>
+        <v>555</v>
       </c>
       <c r="H76" t="n">
-        <v>46.36</v>
+        <v>103.98</v>
       </c>
       <c r="I76" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="J76" t="n">
-        <v>77.6</v>
+        <v>125.35</v>
       </c>
       <c r="K76" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="L76" t="n">
-        <v>110.85</v>
+        <v>119.07</v>
       </c>
       <c r="M76" t="s">
-        <v>542</v>
+        <v>375</v>
       </c>
       <c r="N76" t="n">
-        <v>46.36</v>
+        <v>103.98</v>
       </c>
       <c r="O76" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="P76" t="n">
-        <v>26.69</v>
+        <v>17.32</v>
       </c>
       <c r="Q76" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>434</v>
       </c>
       <c r="C77" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="D77" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E77" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F77" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="G77" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="H77" t="n">
-        <v>44.91</v>
+        <v>96.9</v>
       </c>
       <c r="I77" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="J77" t="n">
-        <v>77.03</v>
+        <v>124.75</v>
       </c>
       <c r="K77" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="L77" t="n">
-        <v>110.83</v>
+        <v>119.37</v>
       </c>
       <c r="M77" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="N77" t="n">
-        <v>44.91</v>
+        <v>96.9</v>
       </c>
       <c r="O77" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="P77" t="n">
-        <v>19.82</v>
+        <v>10.06</v>
       </c>
       <c r="Q77" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s">
-        <v>322</v>
+        <v>434</v>
       </c>
       <c r="C78" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="D78" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E78" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="F78" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="G78" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="H78" t="n">
-        <v>44.57</v>
+        <v>103.11</v>
       </c>
       <c r="I78" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="J78" t="n">
-        <v>77.14</v>
+        <v>125.06</v>
       </c>
       <c r="K78" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="L78" t="n">
-        <v>108.72</v>
+        <v>111.14</v>
       </c>
       <c r="M78" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="N78" t="n">
-        <v>44.57</v>
+        <v>103.11</v>
       </c>
       <c r="O78" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="P78" t="n">
-        <v>13.95</v>
+        <v>28.27</v>
       </c>
       <c r="Q78" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="D79" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E79" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F79" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="G79" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="H79" t="n">
-        <v>45.17</v>
+        <v>101.96</v>
       </c>
       <c r="I79" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="J79" t="n">
-        <v>75.58</v>
+        <v>125.13</v>
       </c>
       <c r="K79" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="L79" t="n">
-        <v>112.34</v>
+        <v>119.63</v>
       </c>
       <c r="M79" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="N79" t="n">
-        <v>45.17</v>
+        <v>101.96</v>
       </c>
       <c r="O79" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="P79" t="n">
-        <v>29.22</v>
+        <v>21.61</v>
       </c>
       <c r="Q79" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>452</v>
       </c>
       <c r="C80" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="D80" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E80" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="F80" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="G80" t="s">
-        <v>394</v>
+        <v>151</v>
       </c>
       <c r="H80" t="n">
-        <v>46.6</v>
+        <v>106.17</v>
       </c>
       <c r="I80" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="J80" t="n">
-        <v>78.33</v>
+        <v>125.94</v>
       </c>
       <c r="K80" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="L80" t="n">
-        <v>113.71</v>
+        <v>127.9</v>
       </c>
       <c r="M80" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="N80" t="n">
-        <v>46.6</v>
+        <v>106.17</v>
       </c>
       <c r="O80" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="P80" t="n">
-        <v>28.66</v>
+        <v>15.08</v>
       </c>
       <c r="Q80" t="s">
-        <v>565</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -6322,42 +6364,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="B1" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="B2" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="B3" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="B4" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B5" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
